--- a/daily/2026-04-04.xlsx
+++ b/daily/2026-04-04.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,7 +708,7 @@
         <v>11</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>11</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
@@ -899,62 +899,66 @@
         <v>11.5</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3</v>
+        <v>13.3</v>
       </c>
       <c r="F6" t="n">
-        <v>9.4</v>
+        <v>12.4</v>
       </c>
       <c r="G6" t="n">
-        <v>15.7</v>
+        <v>13.1</v>
       </c>
       <c r="H6" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>13.6</v>
       </c>
       <c r="J6" t="n">
-        <v>29.6</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>26.9</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>42.5</v>
+        <v>39.4</v>
       </c>
       <c r="M6" t="n">
-        <v>36.7</v>
+        <v>43.9</v>
       </c>
       <c r="N6" t="n">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="O6" t="n">
+        <v>50</v>
+      </c>
+      <c r="P6" t="n">
         <v>60</v>
       </c>
-      <c r="P6" t="n">
-        <v>30</v>
-      </c>
       <c r="Q6" t="n">
-        <v>-0.5</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>5.8</v>
+        <v>-4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>-2</v>
       </c>
       <c r="U6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>9.2 (4g)</t>
+        </is>
+      </c>
       <c r="X6" t="n">
-        <v>-0.5</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="7">
@@ -1028,7 +1032,7 @@
         <v>11</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1059,58 +1063,58 @@
         <v>28.5</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>21.2</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>23.6</v>
+        <v>27.5</v>
       </c>
       <c r="H8" t="n">
-        <v>23.1</v>
+        <v>25.8</v>
       </c>
       <c r="I8" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>33.5</v>
+        <v>29.1</v>
       </c>
       <c r="K8" t="n">
-        <v>33.8</v>
+        <v>29.7</v>
       </c>
       <c r="L8" t="n">
-        <v>48.5</v>
+        <v>51.6</v>
       </c>
       <c r="M8" t="n">
-        <v>47.6</v>
+        <v>50.2</v>
       </c>
       <c r="N8" t="n">
-        <v>5.7</v>
+        <v>8.9</v>
       </c>
       <c r="O8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>-3.5</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="U8" t="n">
         <v>20</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
@@ -1188,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1301,58 +1305,58 @@
         <v>17.5</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="F11" t="n">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="G11" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="H11" t="n">
-        <v>18.2</v>
+        <v>16.7</v>
       </c>
       <c r="I11" t="n">
-        <v>17.8</v>
+        <v>16.4</v>
       </c>
       <c r="J11" t="n">
-        <v>31.9</v>
+        <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="L11" t="n">
-        <v>45.3</v>
+        <v>48.7</v>
       </c>
       <c r="M11" t="n">
-        <v>43.3</v>
+        <v>49.7</v>
       </c>
       <c r="N11" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="O11" t="n">
         <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="U11" t="n">
         <v>11</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1434,7 +1438,7 @@
         <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1690,89 +1694,89 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WAS @ MIA</t>
+          <t>SAS @ DEN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I16" t="n">
         <v>8.5</v>
       </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10.1</v>
-      </c>
       <c r="J16" t="n">
-        <v>18.5</v>
+        <v>21.4</v>
       </c>
       <c r="K16" t="n">
-        <v>19.5</v>
+        <v>22.4</v>
       </c>
       <c r="L16" t="n">
-        <v>47.1</v>
+        <v>49.6</v>
       </c>
       <c r="M16" t="n">
-        <v>49.8</v>
+        <v>46.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T16" t="n">
         <v>-1.1</v>
       </c>
-      <c r="S16" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-1</v>
-      </c>
       <c r="U16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>10.0 (4g)</t>
+          <t>16.0 (5g)</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>-2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1786,75 +1790,75 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>11.4</v>
+        <v>8.6</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>9.9</v>
       </c>
       <c r="I17" t="n">
-        <v>14.7</v>
+        <v>10.1</v>
       </c>
       <c r="J17" t="n">
-        <v>21.8</v>
+        <v>18.5</v>
       </c>
       <c r="K17" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="L17" t="n">
-        <v>38</v>
+        <v>47.1</v>
       </c>
       <c r="M17" t="n">
-        <v>44.9</v>
+        <v>49.8</v>
       </c>
       <c r="N17" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="O17" t="n">
+        <v>40</v>
+      </c>
+      <c r="P17" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U17" t="n">
         <v>30</v>
       </c>
-      <c r="P17" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>14</v>
-      </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>14.0 (6g)</t>
+          <t>10.0 (4g)</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>0.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1864,79 +1868,79 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>26</v>
+      </c>
+      <c r="L18" t="n">
+        <v>38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>30</v>
+      </c>
+      <c r="P18" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="U18" t="n">
         <v>14</v>
       </c>
-      <c r="F18" t="n">
-        <v>11</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="M18" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>60</v>
-      </c>
-      <c r="P18" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>24</v>
-      </c>
       <c r="V18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>7.8 (4g)</t>
+          <t>14.0 (6g)</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>8.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1950,75 +1954,75 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="E19" t="n">
-        <v>12.3</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>12.2</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="H19" t="n">
-        <v>13.9</v>
+        <v>9.5</v>
       </c>
       <c r="I19" t="n">
-        <v>12.1</v>
+        <v>9.4</v>
       </c>
       <c r="J19" t="n">
-        <v>27.3</v>
+        <v>30.5</v>
       </c>
       <c r="K19" t="n">
-        <v>25.7</v>
+        <v>27.2</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5</v>
+        <v>47.9</v>
       </c>
       <c r="M19" t="n">
-        <v>45.2</v>
+        <v>50.6</v>
       </c>
       <c r="N19" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4</v>
+        <v>-1.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7</v>
+        <v>-2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>10.5 (4g)</t>
+          <t>7.8 (4g)</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2032,75 +2036,75 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="n">
-        <v>17.7</v>
+        <v>12.3</v>
       </c>
       <c r="F20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G20" t="n">
         <v>15.4</v>
       </c>
-      <c r="G20" t="n">
-        <v>14.3</v>
-      </c>
       <c r="H20" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="I20" t="n">
-        <v>13.4</v>
+        <v>12.1</v>
       </c>
       <c r="J20" t="n">
-        <v>32</v>
+        <v>27.3</v>
       </c>
       <c r="K20" t="n">
-        <v>30.5</v>
+        <v>25.7</v>
       </c>
       <c r="L20" t="n">
-        <v>51.8</v>
+        <v>43.5</v>
       </c>
       <c r="M20" t="n">
-        <v>49.1</v>
+        <v>45.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="O20" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P20" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1</v>
+        <v>-0.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>-1.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="U20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>12.0 (4g)</t>
+          <t>10.5 (4g)</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2110,79 +2114,75 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.5</v>
+        <v>15.5</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>17.3</v>
       </c>
       <c r="F21" t="n">
-        <v>26.4</v>
+        <v>18.6</v>
       </c>
       <c r="G21" t="n">
-        <v>27.4</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>23.4</v>
+        <v>15.7</v>
       </c>
       <c r="I21" t="n">
-        <v>24.1</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>34.7</v>
+        <v>31.8</v>
       </c>
       <c r="K21" t="n">
-        <v>35.2</v>
+        <v>29.6</v>
       </c>
       <c r="L21" t="n">
-        <v>58.5</v>
+        <v>48.3</v>
       </c>
       <c r="M21" t="n">
-        <v>48.7</v>
+        <v>47.8</v>
       </c>
       <c r="N21" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P21" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="S21" t="n">
-        <v>9.800000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>19.3 (3g)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2196,55 +2196,55 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>17.7</v>
       </c>
       <c r="F22" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
       <c r="G22" t="n">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="I22" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="J22" t="n">
-        <v>25.7</v>
+        <v>32</v>
       </c>
       <c r="K22" t="n">
-        <v>27.6</v>
+        <v>30.5</v>
       </c>
       <c r="L22" t="n">
-        <v>46.1</v>
+        <v>51.8</v>
       </c>
       <c r="M22" t="n">
-        <v>47.2</v>
+        <v>49.1</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.9</v>
+        <v>1.5</v>
       </c>
       <c r="U22" t="n">
         <v>24</v>
@@ -2254,17 +2254,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>14.4 (5g)</t>
+          <t>12.0 (4g)</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>-0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2274,79 +2274,79 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.5</v>
+        <v>24.5</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>26.3</v>
       </c>
       <c r="F23" t="n">
-        <v>13.2</v>
+        <v>21.6</v>
       </c>
       <c r="G23" t="n">
-        <v>12.6</v>
+        <v>20.2</v>
       </c>
       <c r="H23" t="n">
-        <v>15.2</v>
+        <v>21.2</v>
       </c>
       <c r="I23" t="n">
-        <v>15.1</v>
+        <v>21.4</v>
       </c>
       <c r="J23" t="n">
-        <v>28.5</v>
+        <v>34</v>
       </c>
       <c r="K23" t="n">
-        <v>29.4</v>
+        <v>31.7</v>
       </c>
       <c r="L23" t="n">
-        <v>49.7</v>
+        <v>43.9</v>
       </c>
       <c r="M23" t="n">
-        <v>49.3</v>
+        <v>48.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4</v>
+        <v>-3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.9</v>
+        <v>0.2</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4</v>
+        <v>-4.4</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="V23" t="n">
         <v>11</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>15.7 (3g)</t>
+          <t>19.3 (3g)</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-6.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2356,84 +2356,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="E24" t="n">
-        <v>22.3</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>19.6</v>
+        <v>16.4</v>
       </c>
       <c r="G24" t="n">
-        <v>21.7</v>
+        <v>12.9</v>
       </c>
       <c r="H24" t="n">
-        <v>24.6</v>
+        <v>14.7</v>
       </c>
       <c r="I24" t="n">
-        <v>23.4</v>
+        <v>14.5</v>
       </c>
       <c r="J24" t="n">
-        <v>36.2</v>
+        <v>25.7</v>
       </c>
       <c r="K24" t="n">
-        <v>34.1</v>
+        <v>27.6</v>
       </c>
       <c r="L24" t="n">
-        <v>38.7</v>
+        <v>46.1</v>
       </c>
       <c r="M24" t="n">
-        <v>43.4</v>
+        <v>47.2</v>
       </c>
       <c r="N24" t="n">
         <v>6.2</v>
       </c>
       <c r="O24" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P24" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="Q24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S24" t="n">
         <v>-1.1</v>
       </c>
-      <c r="R24" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-4.7</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>-1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="V24" t="n">
         <v>11</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>36.8 (5g)</t>
+          <t>14.4 (5g)</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>8.800000000000001</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2445,236 +2445,232 @@
         <v>15.5</v>
       </c>
       <c r="E25" t="n">
-        <v>14.7</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>12.6</v>
       </c>
       <c r="H25" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="I25" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="J25" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K25" t="n">
         <v>29.4</v>
       </c>
-      <c r="K25" t="n">
-        <v>31.7</v>
-      </c>
       <c r="L25" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
       <c r="M25" t="n">
-        <v>44.6</v>
+        <v>49.3</v>
       </c>
       <c r="N25" t="n">
-        <v>8.5</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" t="n">
         <v>40</v>
       </c>
-      <c r="P25" t="n">
-        <v>47</v>
-      </c>
       <c r="Q25" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T25" t="n">
         <v>-0.9</v>
       </c>
-      <c r="R25" t="n">
-        <v>2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-2.4</v>
-      </c>
       <c r="U25" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="V25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>11.4 (5g)</t>
+          <t>15.7 (3g)</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>-4.9</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>12.5</v>
       </c>
       <c r="E26" t="n">
-        <v>14.7</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>14.6</v>
+        <v>10.6</v>
       </c>
       <c r="G26" t="n">
-        <v>12.1</v>
+        <v>11.3</v>
       </c>
       <c r="H26" t="n">
-        <v>11.4</v>
+        <v>10.8</v>
       </c>
       <c r="I26" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="J26" t="n">
-        <v>27.2</v>
+        <v>23.2</v>
       </c>
       <c r="K26" t="n">
-        <v>26.2</v>
+        <v>24.1</v>
       </c>
       <c r="L26" t="n">
-        <v>45.5</v>
+        <v>37.1</v>
       </c>
       <c r="M26" t="n">
-        <v>45.6</v>
+        <v>39.2</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P26" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3</v>
+        <v>-1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1</v>
+        <v>-2.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>-0.9</v>
       </c>
       <c r="U26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V26" t="n">
-        <v>18</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>14.2 (6g)</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
-        <v>7.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.5</v>
+        <v>24.5</v>
       </c>
       <c r="E27" t="n">
-        <v>20.7</v>
+        <v>22.3</v>
       </c>
       <c r="F27" t="n">
-        <v>18.8</v>
+        <v>19.6</v>
       </c>
       <c r="G27" t="n">
-        <v>18.9</v>
+        <v>21.7</v>
       </c>
       <c r="H27" t="n">
-        <v>12.3</v>
+        <v>24.6</v>
       </c>
       <c r="I27" t="n">
-        <v>11.2</v>
+        <v>23.4</v>
       </c>
       <c r="J27" t="n">
-        <v>34.7</v>
+        <v>36.2</v>
       </c>
       <c r="K27" t="n">
-        <v>23.9</v>
+        <v>34.1</v>
       </c>
       <c r="L27" t="n">
-        <v>46</v>
+        <v>38.7</v>
       </c>
       <c r="M27" t="n">
-        <v>39.8</v>
+        <v>43.4</v>
       </c>
       <c r="N27" t="n">
         <v>6.2</v>
       </c>
       <c r="O27" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P27" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5.3</v>
+        <v>-1.1</v>
       </c>
       <c r="R27" t="n">
-        <v>7.6</v>
+        <v>-3.8</v>
       </c>
       <c r="S27" t="n">
-        <v>6.2</v>
+        <v>-4.7</v>
       </c>
       <c r="T27" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="V27" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>8.3 (3g)</t>
+          <t>36.8 (5g)</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2684,79 +2680,79 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
       <c r="E28" t="n">
-        <v>12.3</v>
+        <v>14.7</v>
       </c>
       <c r="F28" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>40</v>
+      </c>
+      <c r="P28" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="U28" t="n">
         <v>14</v>
       </c>
-      <c r="G28" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I28" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="L28" t="n">
-        <v>47</v>
-      </c>
-      <c r="M28" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O28" t="n">
-        <v>50</v>
-      </c>
-      <c r="P28" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="S28" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>16</v>
-      </c>
       <c r="V28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>11.6 (7g)</t>
+          <t>11.4 (5g)</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2770,75 +2766,75 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="n">
-        <v>5.7</v>
+        <v>14.7</v>
       </c>
       <c r="F29" t="n">
-        <v>5.8</v>
+        <v>14.6</v>
       </c>
       <c r="G29" t="n">
-        <v>6.1</v>
+        <v>12.1</v>
       </c>
       <c r="H29" t="n">
-        <v>6.8</v>
+        <v>11.4</v>
       </c>
       <c r="I29" t="n">
-        <v>7.8</v>
+        <v>12.3</v>
       </c>
       <c r="J29" t="n">
-        <v>21.3</v>
+        <v>27.2</v>
       </c>
       <c r="K29" t="n">
-        <v>24.3</v>
+        <v>26.2</v>
       </c>
       <c r="L29" t="n">
-        <v>59.9</v>
+        <v>45.5</v>
       </c>
       <c r="M29" t="n">
-        <v>53.2</v>
+        <v>45.6</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P29" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="R29" t="n">
-        <v>-2</v>
+        <v>2.3</v>
       </c>
       <c r="S29" t="n">
-        <v>6.7</v>
+        <v>-0.1</v>
       </c>
       <c r="T29" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>7.0 (3g)</t>
+          <t>14.2 (6g)</t>
         </is>
       </c>
       <c r="X29" t="n">
-        <v>-2.2</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2848,79 +2844,79 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="E30" t="n">
-        <v>12.7</v>
+        <v>20.7</v>
       </c>
       <c r="F30" t="n">
-        <v>12.6</v>
+        <v>18.8</v>
       </c>
       <c r="G30" t="n">
-        <v>12.6</v>
+        <v>18.9</v>
       </c>
       <c r="H30" t="n">
-        <v>14.3</v>
+        <v>12.3</v>
       </c>
       <c r="I30" t="n">
-        <v>15</v>
+        <v>11.2</v>
       </c>
       <c r="J30" t="n">
-        <v>27.8</v>
+        <v>34.7</v>
       </c>
       <c r="K30" t="n">
-        <v>30.9</v>
+        <v>23.9</v>
       </c>
       <c r="L30" t="n">
-        <v>52.2</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>51.9</v>
+        <v>39.8</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="O30" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P30" t="n">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.5</v>
+        <v>-5.3</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.4</v>
+        <v>7.6</v>
       </c>
       <c r="S30" t="n">
-        <v>0.3</v>
+        <v>6.2</v>
       </c>
       <c r="T30" t="n">
-        <v>-3.1</v>
+        <v>10.8</v>
       </c>
       <c r="U30" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V30" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>14.8 (4g)</t>
+          <t>8.3 (3g)</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>-6.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2930,79 +2926,79 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22.5</v>
+        <v>16.5</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>14.7</v>
       </c>
       <c r="F31" t="n">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
       <c r="G31" t="n">
-        <v>24.2</v>
+        <v>20.1</v>
       </c>
       <c r="H31" t="n">
-        <v>23.1</v>
+        <v>18.9</v>
       </c>
       <c r="I31" t="n">
-        <v>21.6</v>
+        <v>16.6</v>
       </c>
       <c r="J31" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="K31" t="n">
-        <v>28.3</v>
+        <v>33.3</v>
       </c>
       <c r="L31" t="n">
-        <v>67.8</v>
+        <v>52.1</v>
       </c>
       <c r="M31" t="n">
-        <v>67</v>
+        <v>44.5</v>
       </c>
       <c r="N31" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
       <c r="O31" t="n">
         <v>60</v>
       </c>
       <c r="P31" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="R31" t="n">
-        <v>2.2</v>
+        <v>-0.8</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="T31" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="U31" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>10.4 (5g)</t>
+          <t>13.0 (3g)</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>8.4</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3016,75 +3012,75 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
       <c r="E32" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="F32" t="n">
-        <v>16.8</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="K32" t="n">
         <v>20.2</v>
       </c>
-      <c r="H32" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="I32" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="J32" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="K32" t="n">
-        <v>38.2</v>
-      </c>
       <c r="L32" t="n">
-        <v>36.6</v>
+        <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>43.4</v>
+        <v>39.9</v>
       </c>
       <c r="N32" t="n">
-        <v>12.9</v>
+        <v>5.9</v>
       </c>
       <c r="O32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P32" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2.7</v>
+        <v>-1.4</v>
       </c>
       <c r="R32" t="n">
-        <v>-10</v>
+        <v>5.9</v>
       </c>
       <c r="S32" t="n">
-        <v>-6.8</v>
+        <v>7.1</v>
       </c>
       <c r="T32" t="n">
-        <v>-1.8</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="V32" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>30.2 (5g)</t>
+          <t>11.6 (7g)</t>
         </is>
       </c>
       <c r="X32" t="n">
-        <v>-2.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3094,79 +3090,79 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="F33" t="n">
-        <v>10.8</v>
+        <v>5.8</v>
       </c>
       <c r="G33" t="n">
-        <v>17.7</v>
+        <v>6.1</v>
       </c>
       <c r="H33" t="n">
-        <v>16.1</v>
+        <v>6.8</v>
       </c>
       <c r="I33" t="n">
-        <v>13.6</v>
+        <v>7.8</v>
       </c>
       <c r="J33" t="n">
-        <v>30.7</v>
+        <v>21.3</v>
       </c>
       <c r="K33" t="n">
-        <v>28.3</v>
+        <v>24.3</v>
       </c>
       <c r="L33" t="n">
-        <v>50</v>
+        <v>59.9</v>
       </c>
       <c r="M33" t="n">
-        <v>48</v>
+        <v>53.2</v>
       </c>
       <c r="N33" t="n">
-        <v>8.9</v>
+        <v>4.1</v>
       </c>
       <c r="O33" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.8</v>
+        <v>-2</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>-3</v>
       </c>
       <c r="U33" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>10.0 (5g)</t>
+          <t>7.0 (3g)</t>
         </is>
       </c>
       <c r="X33" t="n">
-        <v>-4.9</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3176,79 +3172,79 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="E34" t="n">
-        <v>6.7</v>
+        <v>10.7</v>
       </c>
       <c r="F34" t="n">
-        <v>7.4</v>
+        <v>13.2</v>
       </c>
       <c r="G34" t="n">
-        <v>8.5</v>
+        <v>13.3</v>
       </c>
       <c r="H34" t="n">
-        <v>8.699999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="I34" t="n">
-        <v>8.6</v>
+        <v>12.9</v>
       </c>
       <c r="J34" t="n">
-        <v>28.5</v>
+        <v>26.7</v>
       </c>
       <c r="K34" t="n">
-        <v>26</v>
+        <v>28.6</v>
       </c>
       <c r="L34" t="n">
-        <v>52.8</v>
+        <v>54.9</v>
       </c>
       <c r="M34" t="n">
-        <v>52.6</v>
+        <v>46.9</v>
       </c>
       <c r="N34" t="n">
-        <v>3.8</v>
+        <v>6.1</v>
       </c>
       <c r="O34" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="P34" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.2</v>
+        <v>0.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>-1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V34" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>12.3 (3g)</t>
+          <t>14.8 (4g)</t>
         </is>
       </c>
       <c r="X34" t="n">
-        <v>14.1</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Adem Bona</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3258,73 +3254,483 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.5</v>
+        <v>22.5</v>
       </c>
       <c r="E35" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="F35" t="n">
-        <v>4.6</v>
+        <v>23.8</v>
       </c>
       <c r="G35" t="n">
-        <v>5.8</v>
+        <v>24.2</v>
       </c>
       <c r="H35" t="n">
-        <v>6.2</v>
+        <v>23.1</v>
       </c>
       <c r="I35" t="n">
-        <v>5.9</v>
+        <v>21.6</v>
       </c>
       <c r="J35" t="n">
-        <v>16.3</v>
+        <v>32</v>
       </c>
       <c r="K35" t="n">
-        <v>18.1</v>
+        <v>28.3</v>
       </c>
       <c r="L35" t="n">
-        <v>56.2</v>
+        <v>67.8</v>
       </c>
       <c r="M35" t="n">
-        <v>59.1</v>
+        <v>67</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P35" t="n">
         <v>50</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="R35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U35" t="n">
+        <v>15</v>
+      </c>
+      <c r="V35" t="n">
+        <v>23</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>10.4 (5g)</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>27</v>
+      </c>
+      <c r="I36" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>30</v>
+      </c>
+      <c r="P36" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
+      </c>
+      <c r="V36" t="n">
+        <v>17</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>30.2 (5g)</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Quentin Grimes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>50</v>
+      </c>
+      <c r="M37" t="n">
+        <v>48</v>
+      </c>
+      <c r="N37" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>50</v>
+      </c>
+      <c r="P37" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>17</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>10.0 (5g)</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>26</v>
+      </c>
+      <c r="L38" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>30</v>
+      </c>
+      <c r="P38" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>16</v>
+      </c>
+      <c r="V38" t="n">
+        <v>23</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>12.3 (3g)</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Paul Reed</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11</v>
+      </c>
+      <c r="G39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>80</v>
+      </c>
+      <c r="P39" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>21</v>
+      </c>
+      <c r="V39" t="n">
+        <v>23</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>5.8 (5g)</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Adem Bona</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J40" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>30</v>
+      </c>
+      <c r="P40" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="R40" t="n">
         <v>-1.3</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S40" t="n">
         <v>-2.9</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T40" t="n">
         <v>-1.8</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U40" t="n">
         <v>14</v>
       </c>
-      <c r="V35" t="n">
-        <v>15</v>
-      </c>
-      <c r="W35" t="inlineStr">
+      <c r="V40" t="n">
+        <v>17</v>
+      </c>
+      <c r="W40" t="inlineStr">
         <is>
           <t>2.0 (5g)</t>
         </is>
       </c>
-      <c r="X35" t="n">
-        <v>-6.1</v>
+      <c r="X40" t="n">
+        <v>-6</v>
       </c>
     </row>
   </sheetData>
@@ -3338,7 +3744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="12" max="12"/>
@@ -3428,7 +3834,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.554</v>
+        <v>0.552</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -3437,10 +3843,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -3450,7 +3856,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 7.2 pts (L5 vs L30) — supports the OVER. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — Volume, Trend, Context, H2H support the OVER; HR L30, HR L10, Defense dissent. Projection model targets 26.6 pts (2.1 pts above line; 55% blended confidence [T3]). Risk: high variance (σ=13.6) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 7.2 pts (L5 vs L30) — supports the OVER. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — Volume, Trend, Context, H2H support the OVER; HR L30, HR L10, Defense dissent. Projection model targets 26.5 pts (2.0 pts above line; 55% blended confidence [T3]). Risk: high variance (σ=13.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3882,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.613</v>
+        <v>0.609</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -3485,20 +3891,20 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Vassell averages 22.5 pts in 4 meetings (+10.0 vs line) — marginally supports the OVER. H2H avg 9.6 pts above season L30; TS% shifts +5.0% in this matchup. Opponent is average defense (#11) at fast pace (#2). Mixed signals: 5/10 agree (Volume, Context, H2H); counter-signals: HR L30, HR L10, Trend. Projection model targets 16.8 pts (4.3 pts above line; 61% blended confidence [T3]).</t>
+          <t>Vassell averages 22.5 pts in 4 meetings (+10.0 vs line) — marginally supports the OVER. H2H avg 9.6 pts above season L30; TS% shifts +5.0% in this matchup. Opponent is average defense (#11) at fast pace (#3). Mixed signals: 5/10 agree (Volume, Context, H2H); counter-signals: HR L30, HR L10, Trend. Projection model targets 16.7 pts (4.2 pts above line; 60% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3930,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.592</v>
+        <v>0.58</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -3533,20 +3939,20 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4</v>
+        <v>1.435</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Harper's L30 average of 13.0 pts vs the 11.5 line — supports the OVER. Opponent is average defense (#11) at fast pace (#2). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H dissent. Projection model targets 14.1 pts (2.6 pts above line; 59% blended confidence [T2]).</t>
+          <t>Harper's L30 average of 13.0 pts vs the 11.5 line — supports the OVER. Opponent is average defense (#11) at fast pace (#3). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H dissent. Projection model targets 13.6 pts (2.1 pts above line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -3563,16 +3969,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.515</v>
+        <v>0.509</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -3581,20 +3987,20 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>26.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1.333</v>
+        <v>1.385</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Jokić averages 34.8 pts in 4 meetings (+8.3 vs line) — marginally supports the OVER. H2H avg 9.5 pts above season L30; TS% shifts -6.5% in this matchup. Opponent is below-average defense (#18) at above-average pace (#9). Mixed signals: 5/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 27.0 pts (0.5 pts above line; 51% blended confidence [T3]). Risk: only 40% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>[Low conviction — lean only] Jokić averages 34.8 pts in 4 meetings (+8.3 vs line) — marginally supports the lean UNDER. H2H avg 9.5 pts above season L30; TS% shifts -6.5% in this matchup. Opponent is below-average defense (#18) at above-average pace (#9). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Defense, H2H, Pace. Projection model targets 26.3 pts (0.2 pts below line; 50% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
@@ -3620,7 +4026,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.602</v>
+        <v>0.58</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -3629,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
         <v>2.75</v>
@@ -3642,7 +4048,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 average of 11.0 pts vs the 11.5 line — marginally supports the UNDER. FG% +5.8% trending (L10 vs L30); Minutes up 2.7 recently (L10=29.6 vs L30=26.9). Opponent is average defense (#11) at fast pace (#2). Mixed signals: 5/10 agree (Volume, HR L30, Trend); counter-signals: HR L10, H2H, Pace. Projection model targets 6.8 pts (4.7 pts below line; 60% blended confidence [T3]). Risk: high variance (σ=9.1) makes the outcome difficult to call with confidence.</t>
+          <t>Jr. averages 9.2 pts in 4 meetings (-2.3 vs line) — marginally supports the UNDER. H2H avg 4.4 pts below season L30; TS% shifts -3.8% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 8.3 pts (3.2 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=7.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -3668,7 +4074,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.542</v>
+        <v>0.527</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -3677,20 +4083,20 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Fox averages 22.0 pts in 4 meetings (+6.5 vs line) — marginally supports the OVER. H2H avg 5.6 pts above season L30; TS% shifts -9.5% in this matchup. Opponent is average defense (#11) at fast pace (#2). Mixed signals: 4/10 agree (Volume, Context, H2H); counter-signals: HR L30, HR L10, Trend. Projection model targets 17.1 pts (1.6 pts above line; 54% blended confidence [T3]).</t>
+          <t>Fox averages 22.0 pts in 4 meetings (+6.5 vs line) — marginally supports the OVER. H2H avg 5.6 pts above season L30; TS% shifts -9.5% in this matchup. Opponent is average defense (#11) at fast pace (#3). Mixed signals: 4/10 agree (Volume, Context, H2H); counter-signals: HR L30, HR L10, Trend. Projection model targets 16.5 pts (1.0 pts above line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -3712,23 +4118,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.577</v>
+        <v>0.528</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>2.85</v>
@@ -3738,7 +4144,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Wembanyama's L30 of 24.7 pts sits 3.8 below the 28.5 line — supports the UNDER. Opponent is below-average defense (#20) at fast pace (#2). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 27.1 pts (1.4 pts below line; 57% blended confidence [T2]).</t>
+          <t>Wembanyama's L30 of 25.0 pts sits 3.5 below the 28.5 line — marginally supports the UNDER. Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 27.6 pts (0.9 pts below line; 52% blended confidence [T3]). Risk: L3 has surged to 35.0 after a 28-pt outing (10.0 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -3764,7 +4170,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.544</v>
+        <v>0.572</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -3773,10 +4179,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>11.4</v>
+        <v>10.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>3.05</v>
@@ -3786,7 +4192,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Johnson's L30 average of 12.2 pts vs the 12.5 line — marginally supports the UNDER. TS% shifts -8.6% in this matchup; FG% +4.1% trending (L10 vs L30). Opponent is below-average defense (#20) at fast pace (#2). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 11.4 pts (1.1 pts below line; 54% blended confidence [T3]).</t>
+          <t>Johnson's L30 average of 12.2 pts vs the 12.5 line — marginally supports the UNDER. TS% shifts -8.6% in this matchup; FG% +4.1% trending (L10 vs L30). Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 10.2 pts (2.3 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -3812,7 +4218,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.575</v>
+        <v>0.569</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -3821,20 +4227,20 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4</v>
+        <v>1.455</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Braun's L30 average of 11.9 pts vs the 11.5 line — marginally supports the UNDER. H2H avg 1.9 pts below season L30; TS% shifts -18.0% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (HR L30, Context, Defense); counter-signals: Volume, HR L10, Trend. Projection model targets 8.7 pts (2.8 pts below line; 57% blended confidence [T3]).</t>
+          <t>Braun's L30 average of 11.9 pts vs the 11.5 line — marginally supports the UNDER. H2H avg 1.9 pts below season L30; TS% shifts -18.0% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (HR L30, Context, Defense); counter-signals: Volume, HR L10, Trend. Projection model targets 9.0 pts (2.5 pts below line; 56% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -3851,38 +4257,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.535</v>
+        <v>0.555</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.2) — highly predictable output near line — supports the OVER. H2H avg 2.0 pts below season L30; Minutes up 3.2 recently (L10=31.9 vs L30=28.7). Opponent is average defense (#11) at fast pace (#2). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H dissent. Projection model targets 18.3 pts (0.8 pts above line; 53% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 2.2 pts (L5 vs L30) — supports the UNDER. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, Pace dissent. Projection model targets 15.3 pts (2.2 pts below line; 55% blended confidence [T2]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -3904,11 +4310,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.653</v>
+        <v>0.648</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -3917,20 +4323,20 @@
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.357</v>
+        <v>1.364</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Champagnie averages 14.4 pts in 5 meetings (+4.9 vs line) — supports the OVER. H2H avg 3.7 pts above season L30; TS% shifts +4.2% in this matchup. Opponent is below-average defense (#20) at fast pace (#2). Full consensus: 10/10 signals aligned (Volume, HR L30, HR L10, Trend). Projection model targets 14.1 pts (4.6 pts above line; 65% blended confidence [T1_PREMIUM]).</t>
+          <t>Champagnie averages 14.4 pts in 5 meetings (+4.9 vs line) — supports the OVER. H2H avg 3.7 pts above season L30; TS% shifts +4.2% in this matchup. Opponent is below-average defense (#20) at fast pace (#3). Full consensus: 10/10 signals aligned (Volume, HR L30, HR L10, Trend). Projection model targets 13.9 pts (4.4 pts above line; 64% blended confidence [T1]).</t>
         </is>
       </c>
     </row>
@@ -3956,7 +4362,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.582</v>
+        <v>0.57</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
@@ -3965,20 +4371,20 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="K13" t="n">
-        <v>1.408</v>
+        <v>1.417</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Brown's L30 of 8.5 pts sits 2.0 above the 6.5 line — supports the OVER. TS% shifts -6.0% in this matchup; FG% +3.6% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Min Trend dissent. Projection model targets 8.8 pts (2.3 pts above line; 58% blended confidence [T3]).</t>
+          <t>Brown's L30 of 8.5 pts sits 2.0 above the 6.5 line — supports the OVER. TS% shifts -6.0% in this matchup; FG% +3.6% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, Min Trend dissent. Projection model targets 8.3 pts (1.8 pts above line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4410,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.584</v>
+        <v>0.578</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
@@ -4013,20 +4419,20 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="K14" t="n">
-        <v>1.357</v>
+        <v>1.435</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Johnson averages 20.0 pts in 3 meetings (+7.5 vs line) — supports the OVER. H2H avg 7.6 pts above season L30; TS% shifts +20.1% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — HR L10, Trend, Context, H2H support the OVER; Volume, HR L30, Defense dissent. Projection model targets 15.6 pts (3.1 pts above line; 58% blended confidence [T2]).</t>
+          <t>Johnson averages 20.0 pts in 3 meetings (+7.5 vs line) — supports the OVER. H2H avg 7.6 pts above season L30; TS% shifts +20.1% in this matchup. Opponent is strong defense (#8) at above-average pace (#9). 6/10 signals agree — HR L10, Trend, Context, H2H support the OVER; Volume, HR L30, Defense dissent. Projection model targets 15.3 pts (2.8 pts above line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4458,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.514</v>
+        <v>0.516</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -4061,10 +4467,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
@@ -4074,62 +4480,62 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.0 pts (L5 vs L30) — marginally supports the UNDER. FG% -4.4% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.5 pts (1.0 pts below line; 51% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 2.0 pts (L5 vs L30) — marginally supports the UNDER. FG% -4.4% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.4 pts (1.1 pts below line; 51% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WAS @ MIA</t>
+          <t>SAS @ DEN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.543</v>
+        <v>0.657</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>11.6</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="K16" t="n">
-        <v>1.385</v>
+        <v>1.709</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.7) — highly predictable output near line — marginally supports the UNDER. Opponent is weak defense (#30) at above-average pace (#11). Mixed signals: 4/10 agree (HR L10, Trend, FG Trend); counter-signals: Volume, HR L30, Context. Projection model targets 7.9 pts (0.6 pts below line; 54% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Barnes averages 16.0 pts in 5 meetings (+9.5 vs line) — supports the OVER. H2H avg 7.5 pts above season L30; FG% +3.4% trending (L10 vs L30). Opponent is below-average defense (#20) at fast pace (#3). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 11.6 pts (5.1 pts above line; 65% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4139,7 +4545,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4148,36 +4554,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.515</v>
+        <v>0.532</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>13.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>0.2</v>
       </c>
       <c r="J17" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="K17" t="n">
-        <v>1.417</v>
+        <v>1.465</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending down 5.9 pts (L5 vs L30) — marginally supports the lean UNDER. FG% -6.9% trending (L10 vs L30); Minutes down 4.2 recently (L10=21.8 vs L30=26.0). Opponent is average defense (#14) at fast pace (#3). Mixed signals: 5/10 agree (HR L10, Trend, Defense); counter-signals: Volume, HR L30, Context. Projection model targets 13.3 pts (0.2 pts below line; 51% blended confidence [T3_LEAN]). Risk: high variance (σ=7.3) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Low scoring variance (σ=4.7) — highly predictable output near line — supports the lean OVER. Opponent is weak defense (#30) at above-average pace (#11). 6/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, FG Trend dissent. Projection model targets 8.3 pts (0.2 pts below line; 53% blended confidence [T3_LEAN]). Risk: L3 has dropped to 6.0 (4.1 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4196,7 +4602,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.528</v>
+        <v>0.517</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -4205,27 +4611,27 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.417</v>
+        <v>1.364</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Mitchell averages 7.8 pts in 4 meetings (-2.7 vs line) — marginally supports the UNDER. H2H avg 1.6 pts below season L30; TS% shifts +8.6% in this matchup. Opponent is weak defense (#24) at above-average pace (#11). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.5 pts (1.0 pts below line; 52% blended confidence [T3]). Risk: L3 has surged to 14.0 after a 7-pt outing (4.6 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending down 5.9 pts (L5 vs L30) — marginally supports the UNDER. FG% -6.9% trending (L10 vs L30); Minutes down 4.2 recently (L10=21.8 vs L30=26.0). Opponent is average defense (#14) at fast pace (#4). Mixed signals: 5/10 agree (HR L10, Trend, Defense); counter-signals: Volume, HR L30, Context. Projection model targets 13.2 pts (0.3 pts below line; 51% blended confidence [T3]). Risk: high variance (σ=7.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4244,7 +4650,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -4253,27 +4659,27 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="I19" t="n">
         <v>2.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K19" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Coulibaly averages 10.5 pts in 4 meetings (-2.0 vs line) — marginally supports the UNDER. H2H avg 1.6 pts below season L30. Opponent is below-average defense (#22) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.9 pts (2.6 pts below line; 56% blended confidence [T3]). Risk: high variance (σ=7.4) makes the outcome difficult to call with confidence.</t>
+          <t>Mitchell averages 7.8 pts in 4 meetings (-2.7 vs line) — marginally supports the UNDER. H2H avg 1.6 pts below season L30; TS% shifts +8.6% in this matchup. Opponent is weak defense (#24) at above-average pace (#11). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 7.9 pts (2.6 pts below line; 56% blended confidence [T3]). Risk: L3 has surged to 14.0 after a 7-pt outing (4.6 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4283,7 +4689,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4292,7 +4698,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.546</v>
+        <v>0.585</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -4301,27 +4707,27 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>16.9</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>1.345</v>
+        <v>1.364</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Larsson averages 12.0 pts in 4 meetings (-3.5 vs line) — marginally supports the OVER. Opponent is weak defense (#24) at above-average pace (#11). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 16.9 pts (1.4 pts above line; 54% blended confidence [T3]). Risk: only 33% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Coulibaly averages 10.5 pts in 4 meetings (-2.0 vs line) — marginally supports the UNDER. H2H avg 1.6 pts below season L30. Opponent is below-average defense (#22) at fast pace (#4). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 9.0 pts (3.5 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=7.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4331,45 +4737,45 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.665</v>
+        <v>0.614</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="I21" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="K21" t="n">
-        <v>1.364</v>
+        <v>1.4</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Herro averages 19.3 pts in 3 meetings (-5.2 vs line) — marginally supports the UNDER. H2H avg 4.8 pts below season L30; TS% shifts +3.4% in this matchup. Opponent is weak defense (#24) at above-average pace (#11). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 18.4 pts (6.1 pts below line; 66% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 3.6 pts (L5 vs L30) — supports the OVER. Minutes up 2.2 recently (L10=31.8 vs L30=29.6). Opponent is weak defense (#23) at fast pace (#4). 7/10 signals agree — HR L10, Trend, Context, Defense support the OVER; Volume, HR L30, H2H dissent. Projection model targets 19.4 pts (3.9 pts above line; 61% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4379,7 +4785,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4388,36 +4794,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.52</v>
+        <v>0.549</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="K22" t="n">
-        <v>1.357</v>
+        <v>1.4</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 of 14.5 pts sits 2.0 below the 16.5 line — supports the UNDER. Opponent is weak defense (#24) at above-average pace (#11). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Pace dissent. Projection model targets 16.1 pts (0.4 pts below line; 52% blended confidence [T3]).</t>
+          <t>Larsson averages 12.0 pts in 4 meetings (-3.5 vs line) — marginally supports the OVER. Opponent is weak defense (#24) at above-average pace (#11). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.0 pts (1.5 pts above line; 54% blended confidence [T3]). Risk: only 33% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4432,40 +4838,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.579</v>
+        <v>0.752</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>12.7</v>
+        <v>15.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4</v>
+        <v>1.364</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=2.8) — highly predictable output near line — supports the UNDER. TS% shifts -6.6% in this matchup. Opponent is weak defense (#30) at above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 12.7 pts (2.8 pts below line; 57% blended confidence [T2]).</t>
+          <t>Herro averages 19.3 pts in 3 meetings (-5.2 vs line) — supports the UNDER. H2H avg 2.1 pts below season L30; TS% shifts +3.4% in this matchup. Opponent is weak defense (#24) at above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Pace dissent. Projection model targets 15.5 pts (9.0 pts below line; 75% blended confidence [T3]). Risk: L3 has surged to 26.3 after a 22-pt outing (4.9 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4475,7 +4881,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4484,41 +4890,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.721</v>
+        <v>0.547</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>33.5</v>
+        <v>15</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4</v>
+        <v>1.408</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Adebayo averages 36.8 pts in 5 meetings (+12.3 vs line) — marginally supports the OVER. H2H avg 13.4 pts above season L30; TS% shifts +8.8% in this matchup. Opponent is weak defense (#30) at above-average pace (#11). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 33.5 pts (9.0 pts above line; 72% blended confidence [T3]). Risk: only 20% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Jr.'s L30 of 14.5 pts sits 2.0 below the 16.5 line — supports the UNDER. Opponent is weak defense (#24) at above-average pace (#11). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, Pace dissent. Projection model targets 15.0 pts (1.5 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4528,45 +4934,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.595</v>
+        <v>0.62</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="K25" t="n">
-        <v>1.943</v>
+        <v>1.345</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Jr. averages 11.4 pts in 5 meetings (-4.1 vs line) — supports the UNDER. H2H avg 3.2 pts below season L30; TS% shifts -4.9% in this matchup. Opponent is average defense (#14) at moderate pace (#15). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Pace, FG Trend dissent. Projection model targets 11.6 pts (3.9 pts below line; 59% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=2.8) — highly predictable output near line — supports the UNDER. TS% shifts -6.6% in this matchup. Opponent is weak defense (#30) at above-average pace (#11). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 11.0 pts (4.5 pts below line; 62% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4576,50 +4982,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.554</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1.943</v>
+        <v>2.7</v>
       </c>
       <c r="K26" t="n">
-        <v>1.8</v>
+        <v>1.435</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.3 pts (L5 vs L30) — supports the OVER. H2H avg 1.9 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is below-average defense (#21) at moderate pace (#18). 6/10 signals agree — HR L30, Trend, Context, Defense support the OVER; Volume, HR L10, Pace dissent. Projection model targets 14.2 pts (1.7 pts above line; 55% blended confidence [T2]).</t>
+          <t>Low scoring variance (σ=4.8) — highly predictable output near line — marginally supports the OVER. Opponent is below-average defense (#22) at fast pace (#4). Mixed signals: 3/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.4 pts (1.9 pts above line; 55% blended confidence [T3]). Risk: only 40% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4628,36 +5034,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.642</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>14.6</v>
+        <v>30.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1.877</v>
+        <v>2.85</v>
       </c>
       <c r="K27" t="n">
-        <v>1.877</v>
+        <v>1.4</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Jenkins averages 8.3 pts in 3 meetings (-8.2 vs line) — marginally supports the UNDER. H2H avg 2.9 pts below season L30; TS% shifts +10.5% in this matchup. Opponent is below-average defense (#16) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 14.6 pts (1.9 pts below line; 55% blended confidence [T3]). Risk: L3 has surged to 20.7 after a 4-pt outing (9.5 above L30) — momentum could push over the under line.</t>
+          <t>Adebayo averages 36.8 pts in 5 meetings (+12.3 vs line) — marginally supports the OVER. H2H avg 13.4 pts above season L30; TS% shifts +8.8% in this matchup. Opponent is weak defense (#30) at above-average pace (#11). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 30.3 pts (5.8 pts above line; 64% blended confidence [T3]). Risk: only 20% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4667,7 +5073,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4676,36 +5082,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.552</v>
+        <v>0.631</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1.943</v>
+        <v>2.75</v>
       </c>
       <c r="K28" t="n">
-        <v>1.8</v>
+        <v>1.417</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 5.9 pts (L5 vs L30) — marginally supports the OVER. H2H avg 3.5 pts above season L30; TS% shifts +3.8% in this matchup. Opponent is below-average defense (#16) at moderate pace (#18). Mixed signals: 5/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.9 pts (1.4 pts above line; 55% blended confidence [T3]). Risk: only 37% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Jr. averages 11.4 pts in 5 meetings (-4.1 vs line) — supports the UNDER. H2H avg 3.2 pts below season L30; TS% shifts -5.2% in this matchup. Opponent is average defense (#14) at moderate pace (#17). 8/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend dissent. Projection model targets 10.1 pts (5.4 pts below line; 63% blended confidence [T3]). Risk: high variance (σ=8.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4715,7 +5121,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4724,36 +5130,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.546</v>
+        <v>0.531</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>7.4</v>
+        <v>13.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
-        <v>1.98</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
-        <v>1.769</v>
+        <v>1.357</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.0 pts (L5 vs L30) — supports the UNDER. FG% +6.7% trending (L10 vs L30); Minutes down 3.0 recently (L10=21.3 vs L30=24.3). Opponent is average defense (#14) at moderate pace (#15). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Pace, FG Trend dissent. Projection model targets 7.4 pts (1.1 pts below line; 54% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 2.3 pts (L5 vs L30) — supports the OVER. H2H avg 1.9 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). 6/10 signals agree — HR L30, Trend, Context, Defense support the OVER; Volume, HR L10, Pace dissent. Projection model targets 13.3 pts (0.8 pts above line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4763,45 +5169,45 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.518</v>
+        <v>0.602</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
-        <v>1.758</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>1.408</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending down 2.4 pts (L5 vs L30) — supports the lean OVER. TS% shifts -6.2% in this matchup; Minutes down 3.1 recently (L10=27.8 vs L30=30.9). Opponent is below-average defense (#21) at moderate pace (#18). 6/10 signals agree — Volume, HR L30, Context, Defense support the OVER; HR L10, Trend, Pace dissent. Projection model targets 13.7 pts (0.2 pts above line; 51% blended confidence [T3_LEAN]). Risk: minutes trending down (27.8 L10 vs 30.9 L30) — role reduction would suppress counting stats.</t>
+          <t>Jenkins averages 8.3 pts in 3 meetings (-8.2 vs line) — marginally supports the UNDER. H2H avg 2.9 pts below season L30; TS% shifts +10.5% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.9 pts (3.6 pts below line; 60% blended confidence [T3]). Risk: L3 has surged to 20.7 after a 4-pt outing (9.5 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4820,36 +5226,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>20.1</v>
+        <v>11.1</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="n">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>1.952</v>
+        <v>1.357</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Duren averages 10.4 pts in 5 meetings (-12.1 vs line) — marginally supports the UNDER. H2H avg 11.2 pts below season L30; TS% shifts +8.4% in this matchup. Opponent is average defense (#15) at moderate pace (#18). Mixed signals: 4/10 agree (Volume, Context, H2H); counter-signals: HR L30, HR L10, Trend. Projection model targets 20.1 pts (2.4 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
+          <t>Edgecombe averages 13.0 pts in 3 meetings (-3.5 vs line) — supports the UNDER. H2H avg 3.6 pts below season L30; TS% shifts -9.9% in this matchup. Opponent is elite defense (#4) at moderate pace (#17). 6/10 signals agree — HR L30, Trend, Context, Defense support the UNDER; Volume, HR L10, FG Trend dissent. Projection model targets 11.1 pts (5.4 pts below line; 62% blended confidence [T3]). Risk: high variance (σ=10.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4859,45 +5265,45 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>27.8</v>
+        <v>9.6</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="K32" t="n">
-        <v>1.769</v>
+        <v>1.435</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 10.0 pts (L5 vs L30) — supports the UNDER. H2H avg 3.4 pts above season L30; FG% -6.8% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#15). 7/10 signals agree — Volume, HR L10, Trend, Context support the UNDER; HR L30, H2H, Pace dissent. Projection model targets 27.8 pts (1.7 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=12.9) makes the outcome difficult to call with confidence.</t>
+          <t>[Low conviction — lean only] Recent scoring trending up 5.9 pts (L5 vs L30) — marginally supports the lean OVER. H2H avg 3.5 pts above season L30; TS% shifts +3.8% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 5/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.6 pts (0.1 pts above line; 52% blended confidence [T3_LEAN]). Risk: only 37% hit rate over L30 suggests the line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4916,36 +5322,36 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
-        <v>1.877</v>
+        <v>2.85</v>
       </c>
       <c r="K33" t="n">
-        <v>1.877</v>
+        <v>1.4</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.8 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.6 pts below season L30; TS% shifts -4.9% in this matchup. Opponent is elite defense (#4) at moderate pace (#15). Mixed signals: 3/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.8 pts (2.7 pts below line; 56% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 2.0 pts (L5 vs L30) — supports the UNDER. FG% +6.7% trending (L10 vs L30); Minutes down 3.0 recently (L10=21.3 vs L30=24.3). Opponent is average defense (#14) at moderate pace (#17). 9/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; FG Trend dissents. Projection model targets 7.3 pts (1.2 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4955,7 +5361,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4964,77 +5370,317 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.52</v>
+        <v>0.536</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9.9</v>
+        <v>12.1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
-        <v>1.962</v>
+        <v>2.75</v>
       </c>
       <c r="K34" t="n">
-        <v>1.781</v>
+        <v>1.417</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Thompson averages 12.3 pts in 3 meetings (+2.8 vs line) — marginally supports the OVER. H2H avg 3.7 pts above season L30; TS% shifts +14.1% in this matchup. Opponent is below-average defense (#16) at moderate pace (#18). Mixed signals: 5/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.9 pts (0.4 pts above line; 52% blended confidence [T3]). Risk: only 37% hit rate over L30 suggests the line may be set fairly.</t>
+          <t>Harris's L30 average of 12.9 pts vs the 13.5 line — supports the UNDER. H2H avg 1.9 pts above season L30; TS% shifts -6.2% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, H2H dissent. Projection model targets 12.1 pts (1.4 pts below line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Duren averages 10.4 pts in 5 meetings (-12.1 vs line) — marginally supports the UNDER. H2H avg 11.2 pts below season L30; TS% shifts +8.4% in this matchup. Opponent is average defense (#15) at slow pace (#23). Mixed signals: 4/10 agree (Volume, Context, H2H); counter-signals: HR L30, HR L10, Trend. Projection model targets 18.6 pts (3.9 pts below line; 59% blended confidence [T3]). Risk: high variance (σ=7.2) makes the outcome difficult to call with confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Maxey's L30 of 26.1 pts sits 2.4 below the 28.5 line — supports the UNDER. H2H avg 4.1 pts above season L30. Opponent is elite defense (#4) at moderate pace (#17). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; H2H, FG Trend, Min Trend dissent. Projection model targets 27.2 pts (1.3 pts below line; 56% blended confidence [T2]).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Quentin Grimes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Recent scoring trending down 2.8 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.6 pts below season L30; TS% shifts -4.9% in this matchup. Opponent is elite defense (#4) at moderate pace (#17). Mixed signals: 4/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.2 pts (3.3 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LEAN UNDER</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>T3_LEAN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>[Low conviction — lean only] Thompson averages 12.3 pts in 3 meetings (+2.8 vs line) — supports the lean UNDER. H2H avg 3.7 pts above season L30; TS% shifts +14.1% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, FG Trend dissent. Projection model targets 9.6 pts (0.1 pts above line; 51% blended confidence [T3_LEAN]).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Paul Reed</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.813</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Recent scoring trending up 2.0 pts (L5 vs L30) — supports the OVER. H2H avg 3.2 pts below season L30; TS% shifts -6.8% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace dissent. Projection model targets 7.9 pts (0.4 pts above line; 54% blended confidence [T3]).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Adem Bona</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="F35" t="n">
-        <v>7</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
         <v>2.5</v>
       </c>
-      <c r="I35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1.943</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>Bona averages 2.0 pts in 5 meetings (-3.5 vs line) — supports the UNDER. H2H avg 3.9 pts below season L30; TS% shifts -6.1% in this matchup. Opponent is average defense (#14) at moderate pace (#15). 7/10 signals agree — HR L10, Trend, Context, Defense support the UNDER; Volume, HR L30, Pace dissent. Projection model targets 2.5 pts (3.0 pts below line; 58% blended confidence [T2]).</t>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.476</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Bona averages 2.0 pts in 5 meetings (-4.5 vs line) — supports the UNDER. H2H avg 3.9 pts below season L30; TS% shifts -6.0% in this matchup. Opponent is average defense (#14) at moderate pace (#17). Full consensus: 10/10 signals aligned (Volume, HR L30, HR L10, Trend). Projection model targets 2.5 pts (4.0 pts below line; 63% blended confidence [T1]).</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5177,7 +5823,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -5297,7 +5943,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5387,27 +6033,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kel'el Ware</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WAS @ MIA</t>
+          <t>SAS @ DEN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alex Sarr</t>
+          <t>Kel'el Ware</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5417,17 +6063,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Davion Mitchell</t>
+          <t>Alex Sarr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5441,13 +6087,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Davion Mitchell</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5461,13 +6107,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pelle Larsson</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5477,17 +6123,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tyler Herro</t>
+          <t>Will Riley</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5497,17 +6143,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>24.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jaime Jaquez Jr.</t>
+          <t>Pelle Larsson</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,17 +6163,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Andrew Wiggins</t>
+          <t>Tyler Herro</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5541,13 +6187,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bam Adebayo</t>
+          <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5557,22 +6203,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Andrew Wiggins</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5587,12 +6233,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5607,27 +6253,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Bam Adebayo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DET @ PHI</t>
+          <t>WAS @ MIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5637,17 +6283,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5657,17 +6303,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5677,17 +6323,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5701,13 +6347,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>22.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5717,17 +6363,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5741,13 +6387,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5757,31 +6403,131 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Jalen Duren</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Quentin Grimes</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LEAN UNDER</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Paul Reed</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DET @ PHI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Adem Bona</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>5.5</v>
+      <c r="D40" t="n">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-04.xlsx
+++ b/daily/2026-04-04.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -792,7 +810,6 @@
       <c r="V4" t="n">
         <v>3</v>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>2.1</v>
       </c>
@@ -1116,7 +1133,6 @@
       <c r="V8" t="n">
         <v>3</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>1.3</v>
       </c>
@@ -1686,7 +1702,6 @@
       <c r="V15" t="n">
         <v>9</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>0</v>
       </c>
@@ -2174,7 +2189,6 @@
       <c r="V21" t="n">
         <v>4</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>4.8</v>
       </c>
@@ -2580,7 +2594,6 @@
       <c r="V26" t="n">
         <v>4</v>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
         <v>14</v>
       </c>
@@ -5751,783 +5764,1773 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Murray scored 15 pts vs 24.5 line (-9.5), OVER missed by 9.5 pts. Murray played 46 min (+9.4 vs L10 avg of 36.4) — 26% more than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 46.3%). Counter-signals that proved correct: HR L30, HR L10, Defense, FG Trend. Signals that were wrong: Volume, Trend, Context. Projection model targeted 26.5 pts — actual 15 was 11.5 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when DEN is involved.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Vassell scored 18 pts vs 12.5 line (+5.5), OVER hit by 5.5 pts. Vassell played 39 min (+9.9 vs L10 avg of 29.3) — 34% more than expected. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 42.0%). Signals that called it correctly: Volume, Context, H2H, Pace, Min Trend (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 16.7 pts — actual 18 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Vassell in this role.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Harper scored 12 pts vs 11.5 line (+0.5), OVER hit by 0.5 pts. Harper played 20 min (-3.7 vs L10 avg of 23.9) — 15% less than expected. Shooting efficiency was hot: 71.4% FG (+14.1% vs L10 avg of 57.3%). 5/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, H2H. Projection model targeted 13.6 pts — actual 12 was 1.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jokić scored 40 pts vs 26.5 line (+13.5), UNDER missed by 13.5 pts. Jokić played 44 min (+8.0 vs L10 avg of 36.0) — 22% more than expected. Shooting was in line with averages: 52.0% FG (13/25, L10 avg 56.7%). Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 26.3 pts — actual 40 was 13.7 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when DEN is involved.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 10 pts vs 11.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 26 played vs L10 avg 24.0. Shooting efficiency was hot: 50.0% FG (+10.6% vs L10 avg of 39.4%). 3/6 from the field. Signals that called it correctly: Trend, Defense, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.3 pts — actual 10 was 1.7 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jr. in this role.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Fox scored 14 pts vs 15.5 line (-1.5), OVER missed by 1.5 pts. Fox played 40 min (+13.2 vs L10 avg of 27.2) — 49% more than expected. Shooting efficiency was cold: 36.8% FG (-12.3% vs L10 avg of 49.1%). 7/19 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, H2H. Projection model targeted 16.5 pts — actual 14 was 2.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Wembanyama scored 34 pts vs 28.5 line (+5.5), UNDER missed by 5.5 pts. Wembanyama played 40 min (+10.5 vs L10 avg of 29.1) — 36% more than expected. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 51.6%). Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 27.6 pts — actual 34 was 6.4 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Wembanyama's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 10 pts vs 12.5 line (-2.5), UNDER hit by 2.5 pts. Johnson played 17 min (-6.2 vs L10 avg of 23.6) — 26% less than expected. Shooting efficiency was cold: 30.0% FG (-21.6% vs L10 avg of 51.6%). 3/10 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 10.2 pts — actual 10 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Braun scored 21 pts vs 11.5 line (+9.5), UNDER missed by 9.5 pts. Braun played 39 min (+8.7 vs L10 avg of 30.5) — 29% more than expected. Shooting efficiency was cold: 43.8% FG (-15.4% vs L10 avg of 59.2%). 7/16 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Pace. Signals that were wrong: HR L30, Context, Defense. Projection model targeted 9.0 pts — actual 21 was 12.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Castle scored 20 pts vs 17.5 line (+2.5), UNDER missed by 2.5 pts. Castle played 40 min (+10.3 vs L10 avg of 30.0) — 34% more than expected. Shooting was in line with averages: 52.9% FG (9/17, L10 avg 48.7%). Counter-signals that proved correct: HR L10, Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.3 pts — actual 20 was 4.7 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Castle's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Champagnie scored 18 pts vs 9.5 line (+8.5), OVER hit by 8.5 pts. Champagnie played 33 min (+6.4 vs L10 avg of 26.6) — 24% more than expected. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 46.1%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (10/10 aligned). Projection model targeted 13.9 pts — actual 18 was 4.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (10/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 5 pts vs 6.5 line (-1.5), OVER missed by 1.5 pts. Brown played 11 min (-10.6 vs L10 avg of 21.6) — 49% less than expected. Shooting efficiency was cold: 28.6% FG (-23.9% vs L10 avg of 52.5%). 2/7 from the field. Counter-signals that proved correct: Defense, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.3 pts — actual 5 was 3.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Brown for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 17 pts vs 12.5 line (+4.5), OVER hit by 4.5 pts. Johnson played 39 min (+9.1 vs L10 avg of 30.1) — 30% more than expected. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 51.1%). Signals that called it correctly: HR L10, Trend, Context, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Defense. Projection model targeted 15.3 pts — actual 17 was 1.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gordon scored 15 pts vs 14.5 line (+0.5), UNDER missed by 0.5 pts. Gordon played 41 min (+14.4 vs L10 avg of 26.7) — 54% more than expected. Shooting efficiency was hot: 58.3% FG (+18.3% vs L10 avg of 40.0%). 7/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, H2H. Signals that were wrong: Trend, Context, Defense. Projection model targeted 13.4 pts — actual 15 was 1.6 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Harrison Barnes</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barnes scored 8 pts vs 6.5 line (+1.5), OVER hit by 1.5 pts. Barnes played 16 min (-4.9 vs L10 avg of 21.4) — 23% less than expected. Shooting efficiency was hot: 75.0% FG (+25.4% vs L10 avg of 49.6%). 3/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 11.6 pts — actual 8 was 3.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Kel'el Ware</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Ware scored 24 pts vs 8.5 line (+15.5), OVER hit by 15.5 pts. Ware played 36 min (+17.3 vs L10 avg of 18.5) — 94% more than expected. Shooting efficiency was hot: 66.7% FG (+19.6% vs L10 avg of 47.1%). 10/15 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 8.3 pts — actual 24 was 15.7 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Ware's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Alex Sarr</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Mitchell scored 12 pts vs 10.5 line (+1.5), UNDER missed by 1.5 pts. Mitchell played 26 min (-4.9 vs L10 avg of 30.5) — 16% less than expected. Shooting efficiency was hot: 55.6% FG (+7.7% vs L10 avg of 47.9%). 5/9 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.9 pts — actual 12 was 4.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Mitchell for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Coulibaly scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 25 played vs L10 avg 27.3. Shooting efficiency was cold: 38.5% FG (-5.0% vs L10 avg of 43.5%). 5/13 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.0 pts — actual 12 was 3.0 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Coulibaly's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Riley scored 31 pts vs 15.5 line (+15.5), OVER hit by 15.5 pts. Riley played 37 min (+5.1 vs L10 avg of 31.8) — 16% more than expected. Shooting efficiency was hot: 70.6% FG (+22.3% vs L10 avg of 48.3%). 12/17 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, H2H. Projection model targeted 19.4 pts — actual 31 was 11.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Riley's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Larsson scored 16 pts vs 15.5 line (+0.5), OVER hit by 0.5 pts. Larsson played 24 min (-8.2 vs L10 avg of 32.0) — 26% less than expected. Shooting efficiency was hot: 60.0% FG (+8.2% vs L10 avg of 51.8%). 6/10 from the field. Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.0 pts — actual 16 was 1.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Larsson in this role.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="5" t="n">
         <v>24.5</v>
       </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 32 pts vs 16.5 line (+15.5), UNDER missed by 15.5 pts. Jr. played 32 min (+6.3 vs L10 avg of 25.7) — 25% more than expected. Shooting efficiency was hot: 66.7% FG (+20.6% vs L10 avg of 46.1%). 12/18 from the field. Counter-signals that proved correct: Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.0 pts — actual 32 was 17.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Wiggins scored 21 pts vs 15.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 26 played vs L10 avg 28.5. Shooting efficiency was hot: 63.6% FG (+13.9% vs L10 avg of 49.7%). 7/11 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.0 pts — actual 21 was 10.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Tre Johnson</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 11 pts vs 12.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 25 played vs L10 avg 23.2. Shooting was in line with averages: 38.5% FG (5/13, L10 avg 37.1%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, Pace. Projection model targeted 14.4 pts — actual 11 was 3.4 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Adebayo scored 14 pts vs 24.5 line (-10.5), OVER missed by 10.5 pts. Adebayo played 24 min (-12.0 vs L10 avg of 36.2) — 33% less than expected. Shooting efficiency was hot: 50.0% FG (+11.3% vs L10 avg of 38.7%). 3/6 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 30.3 pts — actual 14 was 16.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Adebayo for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 3 pts vs 15.5 line (-12.5), UNDER hit by 12.5 pts. Jr. played 24 min (-5.1 vs L10 avg of 29.4) — 17% less than expected. Shooting efficiency was cold: 25.0% FG (-23.1% vs L10 avg of 48.1%). 1/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, FG Trend. Projection model targeted 10.1 pts — actual 3 was 7.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Duncan Robinson</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Robinson scored 11 pts vs 12.5 line (-1.5), OVER missed by 1.5 pts. Robinson played 23 min (-3.8 vs L10 avg of 27.2) — 14% less than expected. Shooting efficiency was hot: 57.1% FG (+11.6% vs L10 avg of 45.5%). 4/7 from the field. Counter-signals that proved correct: Volume, HR L10, Pace, FG Trend. Signals that were wrong: HR L30, Trend, Context. Projection model targeted 13.3 pts — actual 11 was 2.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jenkins scored 16 pts vs 16.5 line (-0.5), UNDER hit by 0.5 pts. Jenkins played 32 min (-3.2 vs L10 avg of 34.7) — 9% less than expected. Shooting efficiency was cold: 36.4% FG (-9.6% vs L10 avg of 46.0%). 4/11 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 12.9 pts — actual 16 was 3.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Jenkins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 19 pts vs 16.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 35 played vs L10 avg 33.5. Shooting efficiency was cold: 38.9% FG (-13.2% vs L10 avg of 52.1%). 7/18 from the field. Counter-signals that proved correct: Volume, HR L10, FG Trend, Min Trend. Signals that were wrong: HR L30, Trend, Context. Projection model targeted 11.1 pts — actual 19 was 7.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Huerter scored 5 pts vs 9.5 line (-4.5), OVER missed by 4.5 pts. Minutes were as expected: 25 played vs L10 avg 23.6. Shooting efficiency was cold: 22.2% FG (-24.8% vs L10 avg of 47.0%). 2/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 9.6 pts — actual 5 was 4.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barlow scored 8 pts vs 8.5 line (-0.5), UNDER hit by 0.5 pts. Barlow played 29 min (+7.7 vs L10 avg of 21.3) — 36% more than expected. Shooting efficiency was cold: 50.0% FG (-9.9% vs L10 avg of 59.9%). 3/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 7.3 pts — actual 8 was 0.7 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Tobias Harris</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E34" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Harris scored 19 pts vs 13.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 27 played vs L10 avg 26.7. Shooting was in line with averages: 53.8% FG (7/13, L10 avg 54.9%). Counter-signals that proved correct: Trend, Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.1 pts — actual 19 was 6.9 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Harris's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Duren scored 16 pts vs 22.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 30 played vs L10 avg 32.0. Shooting efficiency was cold: 62.5% FG (-5.3% vs L10 avg of 67.8%). 5/8 from the field. Signals that called it correctly: Volume, Context, H2H, Pace (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 18.6 pts — actual 16 was 2.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Duren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>28.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Maxey scored 23 pts vs 28.5 line (-5.5), UNDER hit by 5.5 pts. Maxey played 33 min (-4.0 vs L10 avg of 37.2) — 11% less than expected. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 45.3%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: H2H, FG Trend, Min Trend. Projection model targeted 27.2 pts — actual 23 was 4.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Maxey's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Grimes scored 0 pts vs 12.5 line (-12.5), UNDER hit by 12.5 pts. Grimes played 17 min (-13.3 vs L10 avg of 30.7) — 43% less than expected. Shooting efficiency was cold: 0.0% FG (-50.0% vs L10 avg of 50.0%). 0/4 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.2 pts — actual 0 was 9.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Grimes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 14 pts vs 9.5 line (+4.5), UNDER missed by 4.5 pts. Thompson played 25 min (-3.7 vs L10 avg of 28.5) — 13% less than expected. Shooting efficiency was hot: 63.6% FG (+10.8% vs L10 avg of 52.8%). 7/11 from the field. Counter-signals that proved correct: Defense, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.6 pts — actual 14 was 4.4 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Paul Reed</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Reed scored 10 pts vs 7.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 18 played vs L10 avg 17.8. Shooting efficiency was hot: 80.0% FG (+16.2% vs L10 avg of 63.8%). 4/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, Pace. Projection model targeted 7.9 pts — actual 10 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Adem Bona</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>6.5</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bona scored 10 pts vs 6.5 line (+3.5), UNDER missed by 3.5 pts. Bona played 23 min (+6.8 vs L10 avg of 16.3) — 42% more than expected. Shooting efficiency was hot: 100.0% FG (+43.8% vs L10 avg of 56.2%). 5/5 from the field. All 10 agreeing signals (Volume, HR L30, HR L10, Trend) were wrong — result went directly against the consensus. Projection model targeted 2.5 pts — actual 10 was 7.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
       </c>
     </row>
   </sheetData>
